--- a/public/数据表合集/2/p2.xlsx
+++ b/public/数据表合集/2/p2.xlsx
@@ -4,15 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28200" windowHeight="12600" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="京剧剧本_主要角色关系网络总表" sheetId="1" r:id="rId1"/>
-    <sheet name="图2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">京剧剧本_主要角色关系网络总表!$A$1:$J$877</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">图2!$B$1:$B$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5266" uniqueCount="257">
   <si>
     <t>剧本ID</t>
   </si>
@@ -803,18 +801,6 @@
   </si>
   <si>
     <t>王淑英</t>
-  </si>
-  <si>
-    <t>角色总数</t>
-  </si>
-  <si>
-    <t>实际关系数</t>
-  </si>
-  <si>
-    <t>网络密度</t>
-  </si>
-  <si>
-    <t>度中心化</t>
   </si>
 </sst>
 </file>
@@ -1968,9 +1954,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J877"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="10.3833333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="21.4711538461538" customWidth="1"/>
+    <col min="2" max="2" width="21.475" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -30044,502 +30030,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="6"/>
-  <cols>
-    <col min="2" max="2" width="31.4134615384615" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>70002101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>19</v>
-      </c>
-      <c r="E2">
-        <v>88</v>
-      </c>
-      <c r="F2">
-        <v>0.51462</v>
-      </c>
-      <c r="G2">
-        <v>0.480392</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>70002102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>0.581818</v>
-      </c>
-      <c r="G3">
-        <v>0.266667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>70002103</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>175</v>
-      </c>
-      <c r="F4">
-        <v>0.462963</v>
-      </c>
-      <c r="G4">
-        <v>0.299145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>70002104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>56</v>
-      </c>
-      <c r="F5">
-        <v>0.848485</v>
-      </c>
-      <c r="G5">
-        <v>0.181818</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>70002105</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>101</v>
-      </c>
-      <c r="F6">
-        <v>0.480952</v>
-      </c>
-      <c r="G6">
-        <v>0.463158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>70002201</v>
-      </c>
-      <c r="B7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>109</v>
-      </c>
-      <c r="F7">
-        <v>0.43083</v>
-      </c>
-      <c r="G7">
-        <v>0.52381</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>70002202</v>
-      </c>
-      <c r="B8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>62</v>
-      </c>
-      <c r="F8">
-        <v>0.326316</v>
-      </c>
-      <c r="G8">
-        <v>0.51462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>70002203</v>
-      </c>
-      <c r="B9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <v>0.611111</v>
-      </c>
-      <c r="G9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>70002205</v>
-      </c>
-      <c r="B10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10">
-        <v>16</v>
-      </c>
-      <c r="E10">
-        <v>74</v>
-      </c>
-      <c r="F10">
-        <v>0.616667</v>
-      </c>
-      <c r="G10">
-        <v>0.438095</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>70006101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
-        <v>0.833333</v>
-      </c>
-      <c r="G11">
-        <v>0.333333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>70006102</v>
-      </c>
-      <c r="B12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>70006103</v>
-      </c>
-      <c r="B13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>70006104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14">
-        <v>7</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <v>0.47619</v>
-      </c>
-      <c r="G14">
-        <v>0.733333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>70006105</v>
-      </c>
-      <c r="B15" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>70006106</v>
-      </c>
-      <c r="B16" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" t="s">
-        <v>168</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>70006107</v>
-      </c>
-      <c r="B17" t="s">
-        <v>212</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-      <c r="E17">
-        <v>19</v>
-      </c>
-      <c r="F17">
-        <v>0.678571</v>
-      </c>
-      <c r="G17">
-        <v>0.428571</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>70006108</v>
-      </c>
-      <c r="B18" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <v>12</v>
-      </c>
-      <c r="F18">
-        <v>0.571429</v>
-      </c>
-      <c r="G18">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>70006109</v>
-      </c>
-      <c r="B19" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19">
-        <v>7</v>
-      </c>
-      <c r="E19">
-        <v>14</v>
-      </c>
-      <c r="F19">
-        <v>0.666667</v>
-      </c>
-      <c r="G19">
-        <v>0.466667</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>70006111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20">
-        <v>5</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>70006112</v>
-      </c>
-      <c r="B21" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>